--- a/main/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/main/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:11:46+00:00</t>
+    <t>2025-12-02T13:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/main/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T13:49:48+00:00</t>
+    <t>2025-12-03T08:47:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/main/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,25 +60,25 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T08:47:15+00:00</t>
+    <t>2026-06-01T14:15:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ANS (https://esante.gouv.fr)</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/main/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:15:31+00:00</t>
+    <t>2026-06-26T10:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/main/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:07:38+00:00</t>
+    <t>2026-06-26T12:46:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
